--- a/www/terminologies/ValueSet-JDV-J229-ProfessionSante-ROR.xlsx
+++ b/www/terminologies/ValueSet-JDV-J229-ProfessionSante-ROR.xlsx
@@ -8,12 +8,13 @@
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Include #0" r:id="rId4" sheetId="2"/>
+    <sheet name="Include #1" r:id="rId5" sheetId="3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="91">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20220826120000</t>
+    <t>20260330120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-08-26T12:00:00+01:00</t>
+    <t>2026-03-30T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -280,6 +281,12 @@
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/TRE_G15-ProfessionSante/FHIR/TRE-G15-ProfessionSante</t>
+  </si>
+  <si>
+    <t>Infirmier en pratique avancée (IPA)</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/TRE_R356-ProfessionRessource/FHIR/TRE-R356-ProfessionRessource</t>
   </si>
 </sst>
 </file>
@@ -807,4 +814,50 @@
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>27</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>72</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>90</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
 </file>
--- a/www/terminologies/ValueSet-JDV-J229-ProfessionSante-ROR.xlsx
+++ b/www/terminologies/ValueSet-JDV-J229-ProfessionSante-ROR.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="93">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260330120000</t>
+    <t>20260730120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T12:00:00+01:00</t>
+    <t>2026-07-30T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -284,6 +284,12 @@
   </si>
   <si>
     <t>Infirmier en pratique avancée (IPA)</t>
+  </si>
+  <si>
+    <t>132</t>
+  </si>
+  <si>
+    <t>Stomathérapeute</t>
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/TRE_R356-ProfessionRessource/FHIR/TRE-R356-ProfessionRessource</t>
@@ -818,7 +824,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -843,18 +849,26 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>86</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="2">
         <v>87</v>
       </c>
-      <c r="B4" t="s" s="2">
-        <v>90</v>
+      <c r="B5" t="s" s="2">
+        <v>92</v>
       </c>
     </row>
   </sheetData>
